--- a/astro-site/public/dl/kit-tareas-chocolateria/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/04-tareas-perfiles.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Chocolatero" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Dependiente" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Encargado" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chocolatero" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependiente" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Encargado" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Chocolatero'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Dependiente'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Encargado'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,6 +85,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="11">
@@ -169,66 +178,77 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="8" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="9" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="10" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -588,15 +608,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -604,6 +625,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -632,9 +654,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -663,8 +683,25 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -673,18 +710,18 @@
   <sheetPr>
     <tabColor rgb="00FFF3E0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,6 +738,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -897,6 +935,7 @@
       <c r="F13" s="11" t="n"/>
       <c r="G13" s="13" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -1017,6 +1056,7 @@
       <c r="F20" s="11" t="n"/>
       <c r="G20" s="13" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
@@ -1136,6 +1176,26 @@
       <c r="E27" s="12" t="n"/>
       <c r="F27" s="11" t="n"/>
       <c r="G27" s="13" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C28">
+        <f>COUNTIF(E6:E27,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E28">
+        <f>COUNTIF(B6:B27,"?*")</f>
+        <v>18.0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
@@ -1161,12 +1221,26 @@
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G27">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12 E13 E17 E18 E19 E20 E24 E25 E26 E27" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E17 E18 E19 E20 E24 E25 E26 E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1175,18 +1249,18 @@
   <sheetPr>
     <tabColor rgb="00F3E5F5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1203,6 +1277,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1342,6 +1417,7 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="13" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -1481,6 +1557,7 @@
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="13" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -1582,6 +1659,7 @@
       <c r="F24" s="11" t="n"/>
       <c r="G24" s="13" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
@@ -1682,6 +1760,26 @@
       <c r="E30" s="12" t="n"/>
       <c r="F30" s="11" t="n"/>
       <c r="G30" s="13" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C31">
+        <f>COUNTIF(E6:E30,"✓")</f>
+        <v>3.0</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E31">
+        <f>COUNTIF(B6:B30,"?*")</f>
+        <v>19.0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
@@ -1702,18 +1800,32 @@
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A26:G26"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G30">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E28 E29 E30" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E28 E29 E30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1722,18 +1834,18 @@
   <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1750,6 +1862,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1889,6 +2002,7 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="13" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -2009,6 +2123,7 @@
       <c r="F17" s="11" t="n"/>
       <c r="G17" s="13" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
@@ -2109,6 +2224,26 @@
       <c r="E23" s="12" t="n"/>
       <c r="F23" s="11" t="n"/>
       <c r="G23" s="13" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C24">
+        <f>COUNTIF(E6:E23,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E24">
+        <f>COUNTIF(B6:B23,"?*")</f>
+        <v>14.0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
@@ -2134,11 +2269,25 @@
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A26:G26"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G23">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E21 E22 E23" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E21 E22 E23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-chocolateria/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/04-tareas-perfiles.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -687,7 +687,14 @@
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1184,8 +1191,8 @@
         </is>
       </c>
       <c r="C28">
-        <f>COUNTIF(E6:E27,"✓")</f>
-        <v>2.0</v>
+        <f>COUNTIFS(B6:B27,"?*",E6:E27,"✓")-COUNTIFS(B6:B27,"Tarea",E6:E27,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1193,8 +1200,8 @@
         </is>
       </c>
       <c r="E28">
-        <f>COUNTIF(B6:B27,"?*")</f>
-        <v>18.0</v>
+        <f>COUNTIF(B6:B27,"?*")-COUNTIF(B6:B27,"Tarea")-COUNTIF(E6:E27,"N/A")</f>
+        <v>16.0</v>
       </c>
     </row>
     <row r="29">
@@ -1227,8 +1234,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E17 E18 E19 E20 E24 E25 E26 E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E17 E18 E19 E20 E24 E25 E26 E27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1347,7 +1354,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Verificar etiquetado de precios y alérgenos</t>
+          <t>Verificar el etiquetado de cada referencia: precio, precio por kilo si se vende al peso, y los alérgenos declarados (leche, frutos secos, soja, gluten, huevo y sésamo) más las trazas</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -1506,7 +1513,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Gestionar encargos especiales y pedidos por adelantado</t>
+          <t>Gestionar encargos y pedidos por adelantado: al CONFIRMAR el encargo, dejar por escrito alérgenos e intolerancias, unidades, fecha y hora de recogida, precio, señal cobrada y condiciones de cancelación</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -1646,7 +1653,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Vigilar temperatura de tienda (20-22°C ideal)</t>
+          <t>Vigilar la temperatura de la tienda (20-22 °C) y la de la vitrina (16-18 °C): por encima el bombón suda y pierde brillo — anota la lectura: ____ °C</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
@@ -1768,8 +1775,8 @@
         </is>
       </c>
       <c r="C31">
-        <f>COUNTIF(E6:E30,"✓")</f>
-        <v>3.0</v>
+        <f>COUNTIFS(B6:B30,"?*",E6:E30,"✓")-COUNTIFS(B6:B30,"Tarea",E6:E30,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1777,8 +1784,8 @@
         </is>
       </c>
       <c r="E31">
-        <f>COUNTIF(B6:B30,"?*")</f>
-        <v>19.0</v>
+        <f>COUNTIF(B6:B30,"?*")-COUNTIF(B6:B30,"Tarea")-COUNTIF(E6:E30,"N/A")</f>
+        <v>16.0</v>
       </c>
     </row>
     <row r="32">
@@ -1812,8 +1819,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E28 E29 E30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E28 E29 E30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2110,7 +2117,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Verificar cumplimiento de APPCC</t>
+          <t>Verificar cumplimiento de APPCC (si tienes el Pack APPCC, regístralo allí; si no, anótalo junto a la tarea)</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -2232,8 +2239,8 @@
         </is>
       </c>
       <c r="C24">
-        <f>COUNTIF(E6:E23,"✓")</f>
-        <v>2.0</v>
+        <f>COUNTIFS(B6:B23,"?*",E6:E23,"✓")-COUNTIFS(B6:B23,"Tarea",E6:E23,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2241,8 +2248,8 @@
         </is>
       </c>
       <c r="E24">
-        <f>COUNTIF(B6:B23,"?*")</f>
-        <v>14.0</v>
+        <f>COUNTIF(B6:B23,"?*")-COUNTIF(B6:B23,"Tarea")-COUNTIF(E6:E23,"N/A")</f>
+        <v>12.0</v>
       </c>
     </row>
     <row r="25">
@@ -2275,8 +2282,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E21 E22 E23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E21 E22 E23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
